--- a/outputs/E_no_table_letter.xlsx
+++ b/outputs/E_no_table_letter.xlsx
@@ -9,24 +9,26 @@
   <sheets>
     <sheet name="Validation Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Page Audit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Provenance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Read me" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cell Evidence" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Verification" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Constraints" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Repair Proposals" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Correction History" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Join Receipt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validation Report'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Provenance'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cell Evidence'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constraints'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Join Receipt'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +36,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -79,12 +83,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,6 +548,79 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Time UTC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Previous hash</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Event hash</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -644,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.055</v>
+        <v>0.008</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -686,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -728,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -759,6 +839,73 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -807,7 +954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -851,7 +998,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -980,13 +1127,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1002,6 +1149,8 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1070,23 +1219,33 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Location status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Location reason</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1122,7 +1281,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4536bdf6e830efe49a8d0e5d36085023684d11d1464d9694242270fe7f96a8e9</t>
+          <t>95047d8ed4fe822fb49a52caf8b8cddceabb76c363ba92d62678d07042e041b7</t>
         </is>
       </c>
     </row>
@@ -1161,17 +1320,19 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Draft Excel</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>cells with source boxes</t>
+          <t>Non-empty exported cells</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1181,7 +1342,7 @@
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>equations</t>
+          <t>Cells with source boxes</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1191,7 +1352,7 @@
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>equation checks</t>
+          <t>Cells requiring full-page evidence review</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1201,30 +1362,80 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>failed equation checks</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+          <t>Cell source-box coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>proposals with multiple equations</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1291,7 +1502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1362,77 +1573,4 @@
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Time UTC</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Previous hash</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Event hash</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/E_no_table_letter.xlsx
+++ b/outputs/E_no_table_letter.xlsx
@@ -20,15 +20,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validation Report'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Page Audit'!$A$1:$Q$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Join Receipt'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -564,59 +564,65 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Evidence ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Time UTC</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Excel row</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Previous hash</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Event hash</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -627,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -636,12 +642,17 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -677,36 +688,61 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Candidate ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Selection reason</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Selected</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tables</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Cells</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -724,29 +760,52 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.008</v>
+        <v>0.035</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="G2" s="2" t="b">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>p001-c01</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>native-primary</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Highest deterministic candidate key: trusted layout, credible content, structural quality, then validation-adjusted score; plan order breaks exact ties.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>-10000</v>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -766,29 +825,48 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.003</v>
+        <v>0.105</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>p001-c02</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>native-independent-recovery</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>bounded-parallel</t>
+        </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <v>-10000</v>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -808,32 +886,51 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.004</v>
+        <v>0.112</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>words</t>
         </is>
       </c>
-      <c r="G4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>p001-c03</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>native-independent-recovery</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>bounded-parallel</t>
+        </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
         <v>-10000</v>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -998,7 +1095,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.049</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -1105,7 +1202,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+          <t>Ctrl+click a linked data cell for its source box, confidence meaning, original readings, alternatives and correction count.</t>
         </is>
       </c>
     </row>
@@ -1133,105 +1230,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Evidence ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Data sheet</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Excel row</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Working value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Original extracted value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Original source reading</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>x0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>y0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>OCR score</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence type</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Recognition score</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence meaning</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Reading</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Initial reading</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence state</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Location status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Location reason</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Corrections</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Alternative readings</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1281,7 +1432,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>95047d8ed4fe822fb49a52caf8b8cddceabb76c363ba92d62678d07042e041b7</t>
+          <t>4046de508b38c6edfb1c948513f479c794531a494fcaa7e0be5a1d42f7d1025f</t>
         </is>
       </c>
     </row>
